--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH93"/>
+  <dimension ref="A1:BH96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,7 +760,7 @@
         <v>1.69</v>
       </c>
       <c r="G2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H2" t="n">
         <v>4.8</v>
@@ -778,7 +778,7 @@
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
         <v>4.5</v>
@@ -796,7 +796,7 @@
         <v>1.47</v>
       </c>
       <c r="S2" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="T2" t="n">
         <v>1.72</v>
@@ -808,119 +808,119 @@
         <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Z2" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB2" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE2" t="n">
         <v>75</v>
       </c>
       <c r="AF2" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI2" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM2" t="n">
         <v>100</v>
       </c>
       <c r="AN2" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.05</v>
+        <v>16.5</v>
       </c>
       <c r="AQ2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>15.5</v>
       </c>
-      <c r="AR2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BA2" t="n">
-        <v>2.96</v>
+        <v>6.8</v>
       </c>
       <c r="BB2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC2" t="n">
         <v>14.5</v>
       </c>
-      <c r="BC2" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BD2" t="n">
-        <v>22</v>
+        <v>6.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>42</v>
+        <v>6.8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>3.7</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -966,19 +966,19 @@
         <v>3.65</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P3" t="n">
         <v>2.06</v>
@@ -987,134 +987,134 @@
         <v>1.79</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>2.66</v>
+        <v>2.96</v>
       </c>
       <c r="T3" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="U3" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="V3" t="n">
         <v>1.86</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y3" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB3" t="n">
         <v>16.5</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AC3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF3" t="n">
         <v>30</v>
       </c>
-      <c r="AB3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD3" t="n">
+      <c r="AG3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY3" t="n">
         <v>13</v>
       </c>
-      <c r="AE3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF3" t="n">
+      <c r="AZ3" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC3" t="n">
         <v>36</v>
       </c>
-      <c r="AG3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI3" t="n">
+      <c r="BD3" t="n">
         <v>40</v>
       </c>
-      <c r="AJ3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AV3" t="n">
+      <c r="BE3" t="n">
         <v>8</v>
       </c>
-      <c r="AW3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>29</v>
-      </c>
-      <c r="BD3" t="n">
+      <c r="BF3" t="n">
         <v>32</v>
       </c>
-      <c r="BE3" t="n">
-        <v>3</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>30</v>
-      </c>
       <c r="BG3" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -1160,10 +1160,10 @@
         <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
@@ -1205,7 +1205,7 @@
         <v>14.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
         <v>60</v>
@@ -1220,7 +1220,7 @@
         <v>14</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF4" t="n">
         <v>18</v>
@@ -1235,10 +1235,10 @@
         <v>46</v>
       </c>
       <c r="AJ4" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
         <v>42</v>
@@ -1253,7 +1253,7 @@
         <v>28</v>
       </c>
       <c r="AP4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ4" t="n">
         <v>12.5</v>
@@ -1262,7 +1262,7 @@
         <v>17</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.6</v>
+        <v>38</v>
       </c>
       <c r="AT4" t="n">
         <v>11</v>
@@ -1274,41 +1274,41 @@
         <v>11.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE4" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF4" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>16.5</v>
+        <v>7.8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="H5" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="I5" t="n">
         <v>2.22</v>
@@ -1372,7 +1372,7 @@
         <v>2.16</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="G6" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="I6" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -2900,10 +2900,10 @@
         <v>3.65</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K13" t="n">
         <v>4.1</v>
@@ -2939,7 +2939,7 @@
         <v>2.32</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W13" t="n">
         <v>1.94</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="G22" t="n">
         <v>1.6</v>
       </c>
       <c r="H22" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="I22" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="J22" t="n">
-        <v>1.09</v>
+        <v>4.7</v>
       </c>
       <c r="K22" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4667,10 +4667,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.22</v>
+        <v>2.68</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.14</v>
+        <v>1.51</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -4679,10 +4679,10 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4691,116 +4691,116 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="Y22" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB22" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AC22" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AD22" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>16</v>
       </c>
-      <c r="AG22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AK22" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP22" t="n">
-        <v>3.4</v>
+        <v>9</v>
       </c>
       <c r="AQ22" t="n">
-        <v>3.4</v>
+        <v>9</v>
       </c>
       <c r="AR22" t="n">
-        <v>3.55</v>
+        <v>10.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>3.75</v>
+        <v>12</v>
       </c>
       <c r="AT22" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AU22" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AV22" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AW22" t="n">
-        <v>3.55</v>
+        <v>10.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA22" t="n">
-        <v>3.55</v>
+        <v>10.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BC22" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BD22" t="n">
-        <v>19.5</v>
+        <v>8.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>3.55</v>
+        <v>11</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG22" t="n">
-        <v>36</v>
+        <v>10.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G27" t="n">
         <v>1.79</v>
@@ -5616,7 +5616,7 @@
         <v>4.4</v>
       </c>
       <c r="I27" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J27" t="n">
         <v>4.4</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -6025,7 +6025,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q29" t="n">
         <v>2.06</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6580,7 @@
         <v>1.63</v>
       </c>
       <c r="G32" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H32" t="n">
         <v>6</v>
@@ -6607,7 +6607,7 @@
         <v>1.26</v>
       </c>
       <c r="P32" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q32" t="n">
         <v>1.75</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -6801,10 +6801,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.25</v>
+        <v>2.02</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -6977,7 +6977,7 @@
         <v>1.98</v>
       </c>
       <c r="J34" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="K34" t="n">
         <v>4.5</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
         <v>3.35</v>
       </c>
       <c r="G41" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H41" t="n">
         <v>2.14</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -9456,14 +9456,14 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -9478,28 +9478,28 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>AFC Eskilstuna</t>
+          <t>Parnu JK Vaprus</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FC Jarfalla</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>1.04</v>
       </c>
       <c r="G47" t="n">
-        <v>480</v>
+        <v>240</v>
       </c>
       <c r="H47" t="n">
         <v>1.04</v>
       </c>
       <c r="I47" t="n">
-        <v>770</v>
+        <v>240</v>
       </c>
       <c r="J47" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="K47" t="n">
         <v>950</v>
@@ -9508,16 +9508,16 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
         <v>1.01</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>1.24</v>
       </c>
       <c r="Q47" t="n">
         <v>1.01</v>
@@ -9529,10 +9529,10 @@
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -9541,123 +9541,123 @@
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO47" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AV47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AW47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BA47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BD47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG47" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -9672,186 +9672,186 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>AFC Eskilstuna</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>FC Jarfalla</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="G48" t="n">
-        <v>1.61</v>
+        <v>480</v>
       </c>
       <c r="H48" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="I48" t="n">
+        <v>770</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K48" t="n">
+        <v>950</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
         <v>1000</v>
       </c>
-      <c r="J48" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="K48" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO48" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9866,31 +9866,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Parnu JK Vaprus</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Harju JK Laagri</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="G49" t="n">
-        <v>240</v>
+        <v>1.59</v>
       </c>
       <c r="H49" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="I49" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="J49" t="n">
-        <v>1.02</v>
+        <v>2.7</v>
       </c>
       <c r="K49" t="n">
-        <v>950</v>
+        <v>8.4</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -9905,10 +9905,10 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -10123,7 +10123,7 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y50" t="n">
         <v>10.5</v>
@@ -10138,7 +10138,7 @@
         <v>26</v>
       </c>
       <c r="AC50" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD50" t="n">
         <v>9.800000000000001</v>
@@ -10150,7 +10150,7 @@
         <v>60</v>
       </c>
       <c r="AG50" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH50" t="n">
         <v>21</v>
@@ -10174,10 +10174,10 @@
         <v>85</v>
       </c>
       <c r="AO50" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AP50" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ50" t="n">
         <v>9</v>
@@ -10210,7 +10210,7 @@
         <v>17.5</v>
       </c>
       <c r="BA50" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB50" t="n">
         <v>44</v>
@@ -10225,14 +10225,14 @@
         <v>38</v>
       </c>
       <c r="BF50" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BG50" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -10272,10 +10272,10 @@
         <v>3.25</v>
       </c>
       <c r="I51" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="J51" t="n">
-        <v>1.55</v>
+        <v>2.76</v>
       </c>
       <c r="K51" t="n">
         <v>950</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -10651,22 +10651,22 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="G53" t="n">
         <v>2.32</v>
       </c>
       <c r="H53" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="I53" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J53" t="n">
         <v>3.5</v>
       </c>
       <c r="K53" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -10684,7 +10684,7 @@
         <v>1.93</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -11233,22 +11233,22 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="G56" t="n">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="H56" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="I56" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="J56" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="K56" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -11263,10 +11263,10 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -11451,7 +11451,7 @@
         <v>1.05</v>
       </c>
       <c r="N57" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O57" t="n">
         <v>1.25</v>
@@ -11463,7 +11463,7 @@
         <v>1.75</v>
       </c>
       <c r="R57" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S57" t="n">
         <v>2.9</v>
@@ -11514,7 +11514,7 @@
         <v>19.5</v>
       </c>
       <c r="AI57" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ57" t="n">
         <v>22</v>
@@ -11580,17 +11580,17 @@
         <v>7.4</v>
       </c>
       <c r="BE57" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BF57" t="n">
         <v>9.4</v>
       </c>
       <c r="BG57" t="n">
-        <v>40</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -11978,14 +11978,14 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -12000,31 +12000,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>FK Spartak</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FK Javor Ivanjica</t>
+          <t>Istanbulspor</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="G60" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="H60" t="n">
-        <v>1.04</v>
+        <v>2.64</v>
       </c>
       <c r="I60" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="J60" t="n">
-        <v>1.02</v>
+        <v>3.25</v>
       </c>
       <c r="K60" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -12039,10 +12039,10 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -12366,14 +12366,14 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -12388,31 +12388,31 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>FK Spartak</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Istanbulspor</t>
+          <t>FK Javor Ivanjica</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2.28</v>
+        <v>1.04</v>
       </c>
       <c r="G62" t="n">
-        <v>2.9</v>
+        <v>1000</v>
       </c>
       <c r="H62" t="n">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="I62" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="J62" t="n">
-        <v>3.25</v>
+        <v>1.02</v>
       </c>
       <c r="K62" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -12427,10 +12427,10 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -12606,7 +12606,7 @@
         <v>6</v>
       </c>
       <c r="K63" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -12624,7 +12624,7 @@
         <v>2.3</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -12754,14 +12754,14 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -12776,37 +12776,37 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Deportivo</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="G64" t="n">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="H64" t="n">
+        <v>5</v>
+      </c>
+      <c r="I64" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J64" t="n">
         <v>4.3</v>
       </c>
-      <c r="I64" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J64" t="n">
-        <v>3.55</v>
-      </c>
       <c r="K64" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
@@ -12815,10 +12815,10 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
@@ -12827,10 +12827,10 @@
         <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V64" t="n">
         <v>0</v>
@@ -12839,116 +12839,116 @@
         <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI64" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AK64" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AL64" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM64" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN64" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AO64" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AP64" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AR64" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AS64" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT64" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU64" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV64" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AW64" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AX64" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AY64" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ64" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BA64" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB64" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BC64" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BD64" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BE64" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF64" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BG64" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -12979,19 +12979,19 @@
         </is>
       </c>
       <c r="F65" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G65" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H65" t="n">
         <v>2.7</v>
       </c>
-      <c r="G65" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="H65" t="n">
-        <v>2.76</v>
-      </c>
       <c r="I65" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="J65" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K65" t="n">
         <v>3.55</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -13173,7 +13173,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G66" t="n">
         <v>2.24</v>
@@ -13185,7 +13185,7 @@
         <v>4.6</v>
       </c>
       <c r="J66" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K66" t="n">
         <v>3.8</v>
@@ -13336,14 +13336,14 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -13358,37 +13358,37 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Deportivo</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Malaga</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="G67" t="n">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="H67" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="I67" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J67" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="K67" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
@@ -13397,10 +13397,10 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>2.08</v>
+        <v>1.78</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
@@ -13409,10 +13409,10 @@
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V67" t="n">
         <v>0</v>
@@ -13421,116 +13421,116 @@
         <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH67" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AI67" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AJ67" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AK67" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AL67" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AM67" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AN67" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AO67" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AP67" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AQ67" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AR67" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AS67" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AT67" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AU67" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AV67" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AW67" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AX67" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AY67" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AZ67" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BA67" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BB67" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BC67" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BD67" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BE67" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BF67" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BG67" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -13561,22 +13561,22 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="G68" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="H68" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="I68" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="J68" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="K68" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -13591,10 +13591,10 @@
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -13949,13 +13949,13 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="G70" t="n">
         <v>2.52</v>
       </c>
       <c r="H70" t="n">
-        <v>1.69</v>
+        <v>2.82</v>
       </c>
       <c r="I70" t="n">
         <v>5.3</v>
@@ -13964,7 +13964,7 @@
         <v>3.05</v>
       </c>
       <c r="K70" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -14306,14 +14306,14 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>French Ligue 1</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -14328,61 +14328,61 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Academico de Viseu</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Felgueiras</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>2.02</v>
+        <v>1.24</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="R72" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="U72" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="V72" t="n">
         <v>0</v>
@@ -14391,116 +14391,116 @@
         <v>0</v>
       </c>
       <c r="X72" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AH72" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AI72" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AJ72" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AK72" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AL72" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AM72" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AN72" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AO72" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AP72" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AQ72" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AR72" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AS72" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AT72" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AU72" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AV72" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AW72" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AX72" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AY72" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AZ72" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BA72" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BB72" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BC72" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BD72" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BE72" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BF72" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BG72" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -14522,31 +14522,31 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Moreirense</t>
+          <t>Rio Ave</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>7</v>
+        <v>2.52</v>
       </c>
       <c r="G73" t="n">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="H73" t="n">
-        <v>1.55</v>
+        <v>2.84</v>
       </c>
       <c r="I73" t="n">
-        <v>1.62</v>
+        <v>3.15</v>
       </c>
       <c r="J73" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="K73" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -14561,7 +14561,7 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="Q73" t="n">
         <v>1.01</v>
@@ -14694,14 +14694,14 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>French Ligue 1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -14716,28 +14716,28 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Rio Ave</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="G74" t="n">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="H74" t="n">
-        <v>2.78</v>
+        <v>2.34</v>
       </c>
       <c r="I74" t="n">
-        <v>3.15</v>
+        <v>2.38</v>
       </c>
       <c r="J74" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K74" t="n">
         <v>3.65</v>
@@ -14746,31 +14746,31 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P74" t="n">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V74" t="n">
         <v>0</v>
@@ -14779,123 +14779,123 @@
         <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD74" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AG74" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH74" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI74" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK74" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL74" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM74" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN74" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AO74" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AP74" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ74" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR74" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AS74" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT74" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AU74" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV74" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW74" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AX74" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AY74" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AZ74" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA74" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BB74" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BC74" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BD74" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BE74" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF74" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BG74" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -14910,31 +14910,31 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Academico de Viseu</t>
+          <t>Moreirense</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Felgueiras</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -14949,7 +14949,7 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>1.24</v>
+        <v>1.89</v>
       </c>
       <c r="Q75" t="n">
         <v>1.01</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -15664,14 +15664,14 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -15686,31 +15686,31 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Torque</t>
+          <t>Pesaro</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -15725,10 +15725,10 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="Q79" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
@@ -15858,14 +15858,14 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -15880,31 +15880,31 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Pesaro</t>
+          <t>Torque</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -15919,10 +15919,10 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="R80" t="n">
         <v>0</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -16440,14 +16440,14 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -16462,31 +16462,31 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Always Ready</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -16501,7 +16501,7 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q83" t="n">
         <v>1.01</v>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
@@ -16665,7 +16665,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G84" t="n">
         <v>3.2</v>
@@ -16674,7 +16674,7 @@
         <v>2.3</v>
       </c>
       <c r="I84" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J84" t="n">
         <v>3.95</v>
@@ -16692,7 +16692,7 @@
         <v>6.6</v>
       </c>
       <c r="O84" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P84" t="n">
         <v>2.8</v>
@@ -16719,7 +16719,7 @@
         <v>0</v>
       </c>
       <c r="X84" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y84" t="n">
         <v>17.5</v>
@@ -16758,7 +16758,7 @@
         <v>55</v>
       </c>
       <c r="AK84" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL84" t="n">
         <v>34</v>
@@ -16782,10 +16782,10 @@
         <v>17</v>
       </c>
       <c r="AS84" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="AT84" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AU84" t="n">
         <v>8.800000000000001</v>
@@ -16797,7 +16797,7 @@
         <v>17.5</v>
       </c>
       <c r="AX84" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AY84" t="n">
         <v>13</v>
@@ -16809,7 +16809,7 @@
         <v>22</v>
       </c>
       <c r="BB84" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BC84" t="n">
         <v>25</v>
@@ -16821,21 +16821,21 @@
         <v>36</v>
       </c>
       <c r="BF84" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BG84" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>French Ligue 1</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -16845,66 +16845,66 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>16:05:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Always Ready</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="G85" t="n">
-        <v>2.8</v>
+        <v>1000</v>
       </c>
       <c r="H85" t="n">
-        <v>2.74</v>
+        <v>1.04</v>
       </c>
       <c r="I85" t="n">
-        <v>2.86</v>
+        <v>1000</v>
       </c>
       <c r="J85" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="K85" t="n">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>2.04</v>
+        <v>1.24</v>
       </c>
       <c r="Q85" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="R85" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="U85" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V85" t="n">
         <v>0</v>
@@ -16913,123 +16913,123 @@
         <v>0</v>
       </c>
       <c r="X85" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH85" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AI85" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AJ85" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AK85" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AL85" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AM85" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AN85" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AO85" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AP85" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AQ85" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AR85" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AS85" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AT85" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AU85" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV85" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AW85" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AX85" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AY85" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AZ85" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BA85" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BB85" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BC85" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BD85" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BE85" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BF85" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BG85" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>French Ligue 1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -17039,66 +17039,66 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:05:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Famalicao</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F86" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G86" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H86" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I86" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J86" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K86" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N86" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O86" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P86" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R86" t="n">
         <v>1.41</v>
       </c>
-      <c r="G86" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="H86" t="n">
-        <v>10</v>
-      </c>
-      <c r="I86" t="n">
-        <v>12</v>
-      </c>
-      <c r="J86" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K86" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L86" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O86" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P86" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>2</v>
-      </c>
-      <c r="R86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T86" t="n">
-        <v>2.32</v>
+        <v>1.72</v>
       </c>
       <c r="U86" t="n">
-        <v>1.66</v>
+        <v>2.3</v>
       </c>
       <c r="V86" t="n">
         <v>0</v>
@@ -17107,123 +17107,123 @@
         <v>0</v>
       </c>
       <c r="X86" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y86" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z86" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA86" t="n">
-        <v>570</v>
+        <v>48</v>
       </c>
       <c r="AB86" t="n">
-        <v>7</v>
+        <v>12.5</v>
       </c>
       <c r="AC86" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AD86" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE86" t="n">
-        <v>260</v>
+        <v>30</v>
       </c>
       <c r="AF86" t="n">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="AG86" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ86" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK86" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL86" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM86" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO86" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP86" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ86" t="n">
         <v>11</v>
       </c>
-      <c r="AH86" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI86" t="n">
-        <v>220</v>
-      </c>
-      <c r="AJ86" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AK86" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL86" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM86" t="n">
-        <v>290</v>
-      </c>
-      <c r="AN86" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AO86" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP86" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ86" t="n">
+      <c r="AR86" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS86" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT86" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU86" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV86" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW86" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX86" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY86" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ86" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA86" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB86" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC86" t="n">
         <v>20</v>
-      </c>
-      <c r="AR86" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS86" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT86" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU86" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV86" t="n">
-        <v>32</v>
-      </c>
-      <c r="AW86" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX86" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY86" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ86" t="n">
-        <v>28</v>
-      </c>
-      <c r="BA86" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB86" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC86" t="n">
-        <v>14.5</v>
       </c>
       <c r="BD86" t="n">
         <v>8</v>
       </c>
       <c r="BE86" t="n">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="BF86" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="BG86" t="n">
-        <v>9.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -17233,36 +17233,36 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>Famalicao</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2.72</v>
+        <v>1.41</v>
       </c>
       <c r="G87" t="n">
-        <v>2.94</v>
+        <v>1.45</v>
       </c>
       <c r="H87" t="n">
-        <v>2.96</v>
+        <v>10</v>
       </c>
       <c r="I87" t="n">
-        <v>3.15</v>
+        <v>12</v>
       </c>
       <c r="J87" t="n">
-        <v>2.98</v>
+        <v>4.7</v>
       </c>
       <c r="K87" t="n">
-        <v>3.25</v>
+        <v>5.1</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -17271,16 +17271,16 @@
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P87" t="n">
-        <v>1.54</v>
+        <v>1.83</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.58</v>
+        <v>2</v>
       </c>
       <c r="R87" t="n">
         <v>0</v>
@@ -17289,10 +17289,10 @@
         <v>0</v>
       </c>
       <c r="T87" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U87" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V87" t="n">
         <v>0</v>
@@ -17301,123 +17301,123 @@
         <v>0</v>
       </c>
       <c r="X87" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>570</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD87" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AG87" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH87" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI87" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AJ87" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AK87" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AL87" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM87" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="AN87" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AO87" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP87" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AR87" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AS87" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AT87" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AU87" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AV87" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AW87" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AX87" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AY87" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ87" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BA87" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BB87" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC87" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BD87" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE87" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BF87" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BG87" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -17427,36 +17427,36 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>CA Independiente</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cruzeiro MG</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2.16</v>
+        <v>2.72</v>
       </c>
       <c r="G88" t="n">
-        <v>2.34</v>
+        <v>2.94</v>
       </c>
       <c r="H88" t="n">
-        <v>3.7</v>
+        <v>2.96</v>
       </c>
       <c r="I88" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="J88" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="K88" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -17471,10 +17471,10 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.14</v>
+        <v>2.58</v>
       </c>
       <c r="R88" t="n">
         <v>0</v>
@@ -17604,14 +17604,14 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -17621,36 +17621,36 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Progreso</t>
+          <t>Nautico PE</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -17665,10 +17665,10 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>1.76</v>
+        <v>1.25</v>
       </c>
       <c r="Q89" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
@@ -17798,14 +17798,14 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Mexican Liga MX</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -17815,36 +17815,36 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Atletico San Luis</t>
+          <t>Cruzeiro MG</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1.52</v>
+        <v>2.16</v>
       </c>
       <c r="G90" t="n">
-        <v>1.62</v>
+        <v>2.34</v>
       </c>
       <c r="H90" t="n">
-        <v>5.9</v>
+        <v>3.7</v>
       </c>
       <c r="I90" t="n">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
       <c r="J90" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="K90" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -17859,10 +17859,10 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>2.38</v>
+        <v>1.25</v>
       </c>
       <c r="Q90" t="n">
-        <v>1.62</v>
+        <v>2.14</v>
       </c>
       <c r="R90" t="n">
         <v>0</v>
@@ -17992,14 +17992,14 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Mexican Liga MX</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -18009,36 +18009,36 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Progreso</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="G91" t="n">
-        <v>7.8</v>
+        <v>38</v>
       </c>
       <c r="H91" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I91" t="n">
         <v>1.57</v>
       </c>
-      <c r="I91" t="n">
-        <v>1.68</v>
-      </c>
       <c r="J91" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K91" t="n">
-        <v>4.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -18053,10 +18053,10 @@
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="Q91" t="n">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="R91" t="n">
         <v>0</v>
@@ -18186,14 +18186,14 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Mexican Liga MX</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -18208,31 +18208,31 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Atletico Go</t>
+          <t>Atletico San Luis</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -18247,10 +18247,10 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>1.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q92" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
@@ -18380,14 +18380,14 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-02 01:54:58</t>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -18397,36 +18397,36 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atletico Go</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -18444,137 +18444,719 @@
         <v>1.25</v>
       </c>
       <c r="Q93" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" t="n">
+        <v>0</v>
+      </c>
+      <c r="X93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH93" t="inlineStr">
+        <is>
+          <t>2026-04-02 04:14:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Mexican Liga MX</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Queretaro</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Toluca</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>6</v>
+      </c>
+      <c r="G94" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H94" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="I94" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J94" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K94" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" t="n">
+        <v>0</v>
+      </c>
+      <c r="W94" t="n">
+        <v>0</v>
+      </c>
+      <c r="X94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH94" t="inlineStr">
+        <is>
+          <t>2026-04-02 04:14:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G95" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H95" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I95" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="J95" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="K95" t="n">
+        <v>950</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q95" t="n">
         <v>2.26</v>
       </c>
-      <c r="R93" t="n">
-        <v>0</v>
-      </c>
-      <c r="S93" t="n">
-        <v>0</v>
-      </c>
-      <c r="T93" t="n">
-        <v>0</v>
-      </c>
-      <c r="U93" t="n">
-        <v>0</v>
-      </c>
-      <c r="V93" t="n">
-        <v>0</v>
-      </c>
-      <c r="W93" t="n">
-        <v>0</v>
-      </c>
-      <c r="X93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ93" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA93" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB93" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC93" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD93" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE93" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF93" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG93" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH93" t="inlineStr">
-        <is>
-          <t>2026-04-02 01:54:58</t>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" t="n">
+        <v>0</v>
+      </c>
+      <c r="X95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH95" t="inlineStr">
+        <is>
+          <t>2026-04-02 04:14:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" t="n">
+        <v>0</v>
+      </c>
+      <c r="X96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH96" t="inlineStr">
+        <is>
+          <t>2026-04-02 04:14:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-04.xlsx
@@ -832,7 +832,7 @@
         <v>22</v>
       </c>
       <c r="AE2" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF2" t="n">
         <v>12.5</v>
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="AK2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL2" t="n">
         <v>32</v>
       </c>
       <c r="AM2" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN2" t="n">
         <v>9.199999999999999</v>
@@ -874,7 +874,7 @@
         <v>34</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT2" t="n">
         <v>8.800000000000001</v>
@@ -886,7 +886,7 @@
         <v>17</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX2" t="n">
         <v>9.800000000000001</v>
@@ -898,7 +898,7 @@
         <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB2" t="n">
         <v>15</v>
@@ -907,20 +907,20 @@
         <v>14.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF2" t="n">
         <v>7.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -1107,14 +1107,14 @@
         <v>8</v>
       </c>
       <c r="BF3" t="n">
-        <v>32</v>
+        <v>7.4</v>
       </c>
       <c r="BG3" t="n">
         <v>11.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G4" t="n">
         <v>2.5</v>
@@ -1154,28 +1154,28 @@
         <v>2.88</v>
       </c>
       <c r="I4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
         <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
         <v>1.26</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q4" t="n">
         <v>1.77</v>
@@ -1184,7 +1184,7 @@
         <v>1.47</v>
       </c>
       <c r="S4" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="T4" t="n">
         <v>1.66</v>
@@ -1193,7 +1193,7 @@
         <v>2.36</v>
       </c>
       <c r="V4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W4" t="n">
         <v>1.67</v>
@@ -1220,7 +1220,7 @@
         <v>14</v>
       </c>
       <c r="AE4" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
         <v>18</v>
@@ -1253,7 +1253,7 @@
         <v>28</v>
       </c>
       <c r="AP4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>12.5</v>
@@ -1274,7 +1274,7 @@
         <v>11.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>8.4</v>
+        <v>26</v>
       </c>
       <c r="AX4" t="n">
         <v>15.5</v>
@@ -1286,29 +1286,29 @@
         <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.4</v>
+        <v>29</v>
       </c>
       <c r="BC4" t="n">
-        <v>7.8</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="BF4" t="n">
         <v>14.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.8</v>
+        <v>19.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -1357,152 +1357,152 @@
         <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H6" t="n">
         <v>1.79</v>
@@ -1545,158 +1545,158 @@
         <v>1.94</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K6" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
         <v>1.7</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -1745,16 +1745,16 @@
         <v>1000</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P7" t="n">
         <v>1.25</v>
@@ -1763,134 +1763,134 @@
         <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -1939,152 +1939,152 @@
         <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T8" t="n">
         <v>1.01</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
@@ -2133,152 +2133,152 @@
         <v>1000</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T9" t="n">
         <v>1.01</v>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -2327,152 +2327,152 @@
         <v>1000</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P10" t="n">
         <v>1.24</v>
       </c>
       <c r="Q10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T10" t="n">
         <v>1.01</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -2521,152 +2521,152 @@
         <v>950</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P11" t="n">
         <v>1.24</v>
       </c>
       <c r="Q11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T11" t="n">
         <v>1.01</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -2715,152 +2715,152 @@
         <v>1000</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P12" t="n">
         <v>1.24</v>
       </c>
       <c r="Q12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T12" t="n">
         <v>1.01</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
         <v>2.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="R13" t="n">
         <v>1.45</v>
@@ -2948,7 +2948,7 @@
         <v>22</v>
       </c>
       <c r="Y13" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z13" t="n">
         <v>34</v>
@@ -3008,7 +3008,7 @@
         <v>21</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT13" t="n">
         <v>9.6</v>
@@ -3020,7 +3020,7 @@
         <v>13</v>
       </c>
       <c r="AW13" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AX13" t="n">
         <v>12</v>
@@ -3032,7 +3032,7 @@
         <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB13" t="n">
         <v>20</v>
@@ -3044,17 +3044,17 @@
         <v>23</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF13" t="n">
         <v>10</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -3103,152 +3103,152 @@
         <v>1000</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T14" t="n">
         <v>1.01</v>
       </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="G18" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="H18" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I18" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K18" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.84</v>
+        <v>2.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -4058,19 +4058,19 @@
         <v>1.86</v>
       </c>
       <c r="G19" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I19" t="n">
         <v>5.2</v>
       </c>
       <c r="J19" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K19" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4088,7 +4088,7 @@
         <v>1.86</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -4724,7 +4724,7 @@
         <v>18.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
         <v>16</v>
@@ -4742,7 +4742,7 @@
         <v>5.9</v>
       </c>
       <c r="AO22" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
         <v>9</v>
@@ -4751,7 +4751,7 @@
         <v>9</v>
       </c>
       <c r="AR22" t="n">
-        <v>10.5</v>
+        <v>44</v>
       </c>
       <c r="AS22" t="n">
         <v>12</v>
@@ -4787,7 +4787,7 @@
         <v>13</v>
       </c>
       <c r="BD22" t="n">
-        <v>8.6</v>
+        <v>22</v>
       </c>
       <c r="BE22" t="n">
         <v>11</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="G24" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="H24" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>2.48</v>
       </c>
       <c r="J24" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="K24" t="n">
-        <v>950</v>
+        <v>3.8</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.24</v>
+        <v>1.85</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -5222,19 +5222,19 @@
         <v>1.37</v>
       </c>
       <c r="G25" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="H25" t="n">
         <v>7.2</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="J25" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="G26" t="n">
-        <v>1000</v>
+        <v>1.35</v>
       </c>
       <c r="H26" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="I26" t="n">
         <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="K26" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5443,7 +5443,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q26" t="n">
         <v>1.01</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
         <v>1000</v>
       </c>
       <c r="AC27" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD27" t="n">
         <v>1000</v>
@@ -5685,7 +5685,7 @@
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG27" t="n">
         <v>11.5</v>
@@ -5715,28 +5715,28 @@
         <v>38</v>
       </c>
       <c r="AP27" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR27" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AS27" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT27" t="n">
         <v>12</v>
       </c>
       <c r="AU27" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AV27" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AW27" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX27" t="n">
         <v>12</v>
@@ -5745,32 +5745,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ27" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BA27" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB27" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BC27" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BD27" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BE27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG27" t="n">
         <v>6.8</v>
       </c>
-      <c r="BF27" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -5831,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="Q28" t="n">
         <v>1.7</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -6001,13 +6001,13 @@
         <v>1.66</v>
       </c>
       <c r="H29" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I29" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J29" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K29" t="n">
         <v>4.4</v>
@@ -6025,10 +6025,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -6219,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
         <v>3.2</v>
       </c>
       <c r="H31" t="n">
-        <v>2.52</v>
+        <v>2.72</v>
       </c>
       <c r="I31" t="n">
         <v>3.55</v>
@@ -6398,7 +6398,7 @@
         <v>3.15</v>
       </c>
       <c r="K31" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6580,7 @@
         <v>1.63</v>
       </c>
       <c r="G32" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H32" t="n">
         <v>6</v>
@@ -6616,7 +6616,7 @@
         <v>1.48</v>
       </c>
       <c r="S32" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T32" t="n">
         <v>1.84</v>
@@ -6688,10 +6688,10 @@
         <v>16</v>
       </c>
       <c r="AQ32" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AS32" t="n">
         <v>44</v>
@@ -6703,7 +6703,7 @@
         <v>9</v>
       </c>
       <c r="AV32" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW32" t="n">
         <v>34</v>
@@ -6721,7 +6721,7 @@
         <v>34</v>
       </c>
       <c r="BB32" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BC32" t="n">
         <v>14.5</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -6801,10 +6801,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
         <v>2.32</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -7353,22 +7353,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="H36" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="I36" t="n">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="J36" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="K36" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -7383,10 +7383,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
         <v>3.35</v>
       </c>
       <c r="G41" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H41" t="n">
         <v>2.14</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -8908,7 +8908,7 @@
         <v>1.57</v>
       </c>
       <c r="G44" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="H44" t="n">
         <v>4.8</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -9293,22 +9293,22 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="G46" t="n">
-        <v>240</v>
+        <v>3.6</v>
       </c>
       <c r="H46" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="I46" t="n">
-        <v>420</v>
+        <v>2.62</v>
       </c>
       <c r="J46" t="n">
-        <v>1.02</v>
+        <v>3.1</v>
       </c>
       <c r="K46" t="n">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -9323,10 +9323,10 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -9487,22 +9487,22 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="G47" t="n">
-        <v>240</v>
+        <v>3.4</v>
       </c>
       <c r="H47" t="n">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="I47" t="n">
-        <v>240</v>
+        <v>2.9</v>
       </c>
       <c r="J47" t="n">
-        <v>1.02</v>
+        <v>3.35</v>
       </c>
       <c r="K47" t="n">
-        <v>950</v>
+        <v>6.2</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -9517,10 +9517,10 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -9878,7 +9878,7 @@
         <v>1.36</v>
       </c>
       <c r="G49" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="H49" t="n">
         <v>7</v>
@@ -9887,7 +9887,7 @@
         <v>1000</v>
       </c>
       <c r="J49" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="K49" t="n">
         <v>8.4</v>
@@ -9908,7 +9908,7 @@
         <v>1.76</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -10263,22 +10263,22 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="G51" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="H51" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="I51" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="J51" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="K51" t="n">
-        <v>950</v>
+        <v>3.3</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -10657,16 +10657,16 @@
         <v>2.32</v>
       </c>
       <c r="H53" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I53" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J53" t="n">
         <v>3.5</v>
       </c>
       <c r="K53" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -10684,7 +10684,7 @@
         <v>1.93</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G57" t="n">
         <v>1.93</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -11821,7 +11821,7 @@
         <v>4.6</v>
       </c>
       <c r="H59" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="I59" t="n">
         <v>2.54</v>
@@ -11830,7 +11830,7 @@
         <v>3.25</v>
       </c>
       <c r="K59" t="n">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -12024,7 +12024,7 @@
         <v>3.25</v>
       </c>
       <c r="K60" t="n">
-        <v>950</v>
+        <v>5.8</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -12039,7 +12039,7 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="Q60" t="n">
         <v>1.54</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -12215,7 +12215,7 @@
         <v>1.99</v>
       </c>
       <c r="J61" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K61" t="n">
         <v>7</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -12621,7 +12621,7 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q63" t="n">
         <v>1.53</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -12791,13 +12791,13 @@
         <v>1.77</v>
       </c>
       <c r="H64" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I64" t="n">
         <v>5</v>
       </c>
-      <c r="I64" t="n">
-        <v>5.1</v>
-      </c>
       <c r="J64" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K64" t="n">
         <v>4.4</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -12979,10 +12979,10 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="G65" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="H65" t="n">
         <v>2.7</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -13367,22 +13367,22 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G67" t="n">
         <v>2.04</v>
       </c>
       <c r="H67" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I67" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J67" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K67" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -13561,22 +13561,22 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="G68" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H68" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="I68" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="J68" t="n">
         <v>4.1</v>
       </c>
       <c r="K68" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -13591,10 +13591,10 @@
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -13949,13 +13949,13 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="G70" t="n">
         <v>2.52</v>
       </c>
       <c r="H70" t="n">
-        <v>2.82</v>
+        <v>3.4</v>
       </c>
       <c r="I70" t="n">
         <v>5.3</v>
@@ -13964,7 +13964,7 @@
         <v>3.05</v>
       </c>
       <c r="K70" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -13979,7 +13979,7 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="Q70" t="n">
         <v>2.92</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -14143,7 +14143,7 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G71" t="n">
         <v>4.3</v>
@@ -14158,7 +14158,7 @@
         <v>2.7</v>
       </c>
       <c r="K71" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -14788,7 +14788,7 @@
         <v>15.5</v>
       </c>
       <c r="AA74" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AB74" t="n">
         <v>14.5</v>
@@ -14878,7 +14878,7 @@
         <v>38</v>
       </c>
       <c r="BE74" t="n">
-        <v>9.199999999999999</v>
+        <v>70</v>
       </c>
       <c r="BF74" t="n">
         <v>27</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -14949,10 +14949,10 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -15119,7 +15119,7 @@
         <v>5</v>
       </c>
       <c r="H76" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="I76" t="n">
         <v>2.12</v>
@@ -15128,7 +15128,7 @@
         <v>3.55</v>
       </c>
       <c r="K76" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -15322,7 +15322,7 @@
         <v>7</v>
       </c>
       <c r="K77" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -15501,22 +15501,22 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G78" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="H78" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I78" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J78" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="K78" t="n">
-        <v>950</v>
+        <v>5.8</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -15534,7 +15534,7 @@
         <v>2.28</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="U78" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="V78" t="n">
         <v>0</v>
@@ -15570,7 +15570,7 @@
         <v>1000</v>
       </c>
       <c r="AC78" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD78" t="n">
         <v>1000</v>
@@ -15609,7 +15609,7 @@
         <v>1000</v>
       </c>
       <c r="AP78" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="AQ78" t="n">
         <v>12.5</v>
@@ -15618,7 +15618,7 @@
         <v>17</v>
       </c>
       <c r="AS78" t="n">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="AT78" t="n">
         <v>9.6</v>
@@ -15627,10 +15627,10 @@
         <v>6.6</v>
       </c>
       <c r="AV78" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AW78" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="AX78" t="n">
         <v>11</v>
@@ -15642,19 +15642,19 @@
         <v>9.6</v>
       </c>
       <c r="BA78" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="BB78" t="n">
-        <v>2.84</v>
+        <v>17.5</v>
       </c>
       <c r="BC78" t="n">
-        <v>2.76</v>
+        <v>12.5</v>
       </c>
       <c r="BD78" t="n">
-        <v>2.82</v>
+        <v>16.5</v>
       </c>
       <c r="BE78" t="n">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="BF78" t="n">
         <v>6.6</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -15889,13 +15889,13 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="G80" t="n">
         <v>3.85</v>
       </c>
       <c r="H80" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="I80" t="n">
         <v>3.3</v>
@@ -15904,7 +15904,7 @@
         <v>2.9</v>
       </c>
       <c r="K80" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -16665,16 +16665,16 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G84" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H84" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I84" t="n">
         <v>2.3</v>
-      </c>
-      <c r="I84" t="n">
-        <v>2.32</v>
       </c>
       <c r="J84" t="n">
         <v>3.95</v>
@@ -16689,13 +16689,13 @@
         <v>1.03</v>
       </c>
       <c r="N84" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O84" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P84" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q84" t="n">
         <v>1.52</v>
@@ -16734,7 +16734,7 @@
         <v>22</v>
       </c>
       <c r="AC84" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD84" t="n">
         <v>12</v>
@@ -16755,13 +16755,13 @@
         <v>26</v>
       </c>
       <c r="AJ84" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK84" t="n">
         <v>30</v>
       </c>
       <c r="AL84" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM84" t="n">
         <v>46</v>
@@ -16773,7 +16773,7 @@
         <v>10</v>
       </c>
       <c r="AP84" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ84" t="n">
         <v>15.5</v>
@@ -16785,10 +16785,10 @@
         <v>20</v>
       </c>
       <c r="AT84" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AU84" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV84" t="n">
         <v>11</v>
@@ -16803,7 +16803,7 @@
         <v>13</v>
       </c>
       <c r="AZ84" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA84" t="n">
         <v>22</v>
@@ -16815,7 +16815,7 @@
         <v>25</v>
       </c>
       <c r="BD84" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE84" t="n">
         <v>36</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -17059,7 +17059,7 @@
         <v>2.8</v>
       </c>
       <c r="H86" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I86" t="n">
         <v>2.84</v>
@@ -17131,7 +17131,7 @@
         <v>30</v>
       </c>
       <c r="AF86" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG86" t="n">
         <v>12.5</v>
@@ -17146,7 +17146,7 @@
         <v>48</v>
       </c>
       <c r="AK86" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL86" t="n">
         <v>44</v>
@@ -17194,16 +17194,16 @@
         <v>14.5</v>
       </c>
       <c r="BA86" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB86" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC86" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD86" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BC86" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD86" t="n">
-        <v>8</v>
       </c>
       <c r="BE86" t="n">
         <v>65</v>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -17277,7 +17277,7 @@
         <v>1.34</v>
       </c>
       <c r="P87" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q87" t="n">
         <v>2</v>
@@ -17289,10 +17289,10 @@
         <v>0</v>
       </c>
       <c r="T87" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="U87" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V87" t="n">
         <v>0</v>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -17829,7 +17829,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G90" t="n">
         <v>2.34</v>
@@ -17838,7 +17838,7 @@
         <v>3.7</v>
       </c>
       <c r="I90" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J90" t="n">
         <v>3.15</v>
@@ -17859,10 +17859,10 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="R90" t="n">
         <v>0</v>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -18032,7 +18032,7 @@
         <v>1.34</v>
       </c>
       <c r="I91" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="J91" t="n">
         <v>4.4</v>
@@ -18056,7 +18056,7 @@
         <v>1.76</v>
       </c>
       <c r="Q91" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="R91" t="n">
         <v>0</v>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -18220,7 +18220,7 @@
         <v>1.52</v>
       </c>
       <c r="G92" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H92" t="n">
         <v>5.9</v>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -18617,7 +18617,7 @@
         <v>1.66</v>
       </c>
       <c r="J94" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="K94" t="n">
         <v>4.7</v>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -18799,22 +18799,22 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1.09</v>
+        <v>3.9</v>
       </c>
       <c r="G95" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H95" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I95" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="J95" t="n">
-        <v>1.27</v>
+        <v>3.2</v>
       </c>
       <c r="K95" t="n">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -18829,10 +18829,10 @@
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="Q95" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R95" t="n">
         <v>0</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-04-02 04:14:32</t>
+          <t>2026-04-02 06:34:28</t>
         </is>
       </c>
     </row>
